--- a/E-CommerceTestsSelenium/src/test/resources/TestData/FlipkartTestData.xlsx
+++ b/E-CommerceTestsSelenium/src/test/resources/TestData/FlipkartTestData.xlsx
@@ -13,24 +13,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="6">
   <si>
     <t>SearchText</t>
   </si>
   <si>
-    <t>Mobile</t>
+    <t>Watches</t>
   </si>
   <si>
     <t>TV</t>
   </si>
   <si>
-    <t>Speaker</t>
-  </si>
-  <si>
-    <t>Laptop</t>
-  </si>
-  <si>
-    <t>Watches</t>
+    <t>Adidas</t>
   </si>
   <si>
     <t>Nike</t>
@@ -293,7 +287,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
@@ -306,7 +300,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -314,7 +308,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -322,7 +316,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -330,24 +324,11 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>7</v>
-      </c>
+      <c r="A6" s="1"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
